--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_baseline.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_baseline.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2280,6 +2280,118 @@
       <c r="R29" t="inlineStr">
         <is>
           <t>Derived canonical discharge / last-recorded weight (grams) = dischweight (date in datedischweight). Distinct concept from birth weight; never folded into it. Cleaning pipeline Module 15. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Maternal age (years) -- canonical (derived)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>9</v>
+      </c>
+      <c r="Q30">
+        <v>60</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Derived canonical maternal age in years. Cleaning pipeline Module 15 computes coalesce(matageyrs, mat_age_date_years). ZIM captures matageyrs only (matagedate is a Malawi maternity-form field), so in ZIM data this column always equals matageyrs and mat_age_source is always 'matageyrs'; the shared derivation keeps the two countries on one schema. Emitted only where a source column is present. Originals retained. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2578,7 +2690,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Birth Asphyxia/ Hypoxic Ischaemic Encephalopathy (HIE)</t>
+          <t>Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)</t>
         </is>
       </c>
       <c r="D10">
@@ -2938,7 +3050,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Congenital Dislocation of the hip (CDH)</t>
+          <t>Congenital dislocation of the hip (CDH)</t>
         </is>
       </c>
       <c r="D22">
@@ -3268,7 +3380,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Risk factors for sepsis (but sepsis ruled out)</t>
+          <t>Sepsis (risk factors, but ruled out)</t>
         </is>
       </c>
       <c r="D33">
@@ -3298,7 +3410,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mild Talipes (club foot)</t>
+          <t>Talipes MILD (club foot)</t>
         </is>
       </c>
       <c r="D34">
@@ -3688,7 +3800,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Term with RD</t>
+          <t>Respiratory Distress (term baby)</t>
         </is>
       </c>
       <c r="D47">
@@ -3898,7 +4010,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (Symptomatic)</t>
+          <t>Hypoglycaemia (symptomatic)</t>
         </is>
       </c>
       <c r="D54">
@@ -3958,7 +4070,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Physiological Jaundice</t>
+          <t>Jaundice (physiological)</t>
         </is>
       </c>
       <c r="D56">
@@ -4198,7 +4310,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Very Premature (28-31 weeks)</t>
+          <t>Very Premature (28 to 31.6 weeks)</t>
         </is>
       </c>
       <c r="D64">
@@ -4288,7 +4400,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pathological Jaundice</t>
+          <t>Jaundice (pathological)</t>
         </is>
       </c>
       <c r="D67">
@@ -4343,12 +4455,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>ProJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prolonged Jaundice</t>
+          <t>Jaundice (prolonged)</t>
         </is>
       </c>
       <c r="D69">
@@ -4361,7 +4473,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>ProJ</t>
         </is>
       </c>
     </row>
@@ -4553,12 +4665,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>PJaundice</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>Prolonged Jaundice (babies from 21 days of age)</t>
         </is>
       </c>
       <c r="D76">
@@ -4566,12 +4678,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>b30ef9d1-024b-45d8-bcc8-c9ef3331f644</t>
+          <t>947d944e-bc0b-4cf8-be4c-fdff56035020</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>PJaundice</t>
         </is>
       </c>
     </row>
@@ -4583,12 +4695,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Syph_Exp</t>
+          <t>Premature</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Syphilis exposed</t>
+          <t>Premature</t>
         </is>
       </c>
       <c r="D77">
@@ -4596,42 +4708,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>bbbad131-9323-4f6e-9200-ca640bb5bf27</t>
+          <t>b30ef9d1-024b-45d8-bcc8-c9ef3331f644</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Syph_Exp</t>
+          <t>Premature</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>diagdis1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Syph_Exp</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Syphilis exposed</t>
         </is>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5577b2a8-f2f9-4d63-8c8e-0a330677b709</t>
+          <t>bbbad131-9323-4f6e-9200-ca640bb5bf27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Syph_Exp</t>
         </is>
       </c>
     </row>
@@ -4643,25 +4755,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0560751e-e423-43af-ab3f-36f49ca1f4a1</t>
+          <t>5577b2a8-f2f9-4d63-8c8e-0a330677b709</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4673,25 +4785,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Not Sure</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>043061ae-ba3e-420e-bc7c-07ea11d6712d</t>
+          <t>0560751e-e423-43af-ab3f-36f49ca1f4a1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4703,25 +4815,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Unsure</t>
+          <t>Not Sure</t>
         </is>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3d7a5b87-2617-4f75-8963-dbbe741f5e0a</t>
+          <t>043061ae-ba3e-420e-bc7c-07ea11d6712d</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -4733,55 +4845,55 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AmbG</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ambiguous genitalia</t>
+          <t>Unsure</t>
         </is>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>a8aa85ec-beeb-4b4d-92ad-387ae869f97d</t>
+          <t>3d7a5b87-2617-4f75-8963-dbbe741f5e0a</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AmbG</t>
+          <t>U</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>medsdis</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>AmbG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Ambiguous genitalia</t>
         </is>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>a8aa85ec-beeb-4b4d-92ad-387ae869f97d</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>AmbG</t>
         </is>
       </c>
     </row>
@@ -4793,25 +4905,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Folic acid</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>7c699351-2764-4d66-abde-06b29e90d8cb</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -4823,25 +4935,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iron (Ferrous sulphate)</t>
+          <t>Folic acid</t>
         </is>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>58e83e70-6698-4b24-a43a-8b7e9b72c52b</t>
+          <t>7c699351-2764-4d66-abde-06b29e90d8cb</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -4853,25 +4965,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vitamin D</t>
+          <t>Iron (Ferrous sulphate)</t>
         </is>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
+          <t>58e83e70-6698-4b24-a43a-8b7e9b72c52b</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>FE</t>
         </is>
       </c>
     </row>
@@ -4883,25 +4995,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>VITD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Intramuscular procaine penicillin (syphillis)</t>
+          <t>Vitamin D</t>
         </is>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>25878b06-3441-4b58-889c-ec5868fb7f0a</t>
+          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>VITD</t>
         </is>
       </c>
     </row>
@@ -4913,25 +5025,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NVP (Nevirapine)</t>
+          <t>Intramuscular procaine penicillin (syphillis)</t>
         </is>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5b7a2825-6bc4-4de3-9d9f-9358815b877d</t>
+          <t>25878b06-3441-4b58-889c-ec5868fb7f0a</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
@@ -4943,25 +5055,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Amoxicillin</t>
+          <t>NVP (Nevirapine)</t>
         </is>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
+          <t>5b7a2825-6bc4-4de3-9d9f-9358815b877d</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -4973,25 +5085,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>Amox</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AZT (Zidovudine)</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
+          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>Amox</t>
         </is>
       </c>
     </row>
@@ -5003,25 +5115,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>AZT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AZT (Zidovudine)</t>
         </is>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>AZT</t>
         </is>
       </c>
     </row>
@@ -5033,25 +5145,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Amikacin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -5063,25 +5175,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amik</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amikacin</t>
         </is>
       </c>
       <c r="D93">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7a841c62-62c0-4247-a141-68b5120b3cd9</t>
+          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amik</t>
         </is>
       </c>
     </row>
@@ -5098,15 +5210,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BCG Vaccine</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="D94">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
+          <t>7a841c62-62c0-4247-a141-68b5120b3cd9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5123,25 +5235,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>BCG Vaccine</t>
         </is>
       </c>
       <c r="D95">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
+          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BCG</t>
         </is>
       </c>
     </row>
@@ -5153,25 +5265,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cloxacillin</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="D96">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>cff42224-f861-4330-9468-cdc903298e70</t>
+          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CAF</t>
         </is>
       </c>
     </row>
@@ -5183,25 +5295,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Clox</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Folate</t>
+          <t>Cloxacillin</t>
         </is>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
+          <t>cff42224-f861-4330-9468-cdc903298e70</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Clox</t>
         </is>
       </c>
     </row>
@@ -5213,25 +5325,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Folate</t>
         </is>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
+          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -5243,25 +5355,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metronidazole</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D99">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
+          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
@@ -5273,25 +5385,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nevirapine</t>
+          <t>Metronidazole</t>
         </is>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
+          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -5303,25 +5415,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phenobarbitone</t>
+          <t>Nevirapine</t>
         </is>
       </c>
       <c r="D101">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
+          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -5333,25 +5445,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>PHEN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Procaine Penicillin</t>
+          <t>Phenobarbitone</t>
         </is>
       </c>
       <c r="D102">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
+          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>PHEN</t>
         </is>
       </c>
     </row>
@@ -5363,85 +5475,85 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine</t>
+          <t>Procaine Penicillin</t>
         </is>
       </c>
       <c r="D103">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
+          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>medsgiven</t>
+          <t>medsdis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>TTV</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>X penicillin</t>
+          <t>Tetanus Vaccine</t>
         </is>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0a98f906-82dc-4082-917b-4657a612566e</t>
+          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>TTV</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>medsgiven</t>
+          <t>medsdis</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>AZT3TC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gentamicin</t>
+          <t>Zidolam (AZT and 3TC)</t>
         </is>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4f895d9a-7600-44c6-b867-c72af7bd7413</t>
+          <t>2f8946b7-668c-4eca-aef7-217c7378a4f3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>AZT3TC</t>
         </is>
       </c>
     </row>
@@ -5453,25 +5565,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>X-penicillin and gentamicin</t>
+          <t>X penicillin</t>
         </is>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>27e4ad0e-ad3d-4ef1-97d0-7dfff0495574</t>
+          <t>0a98f906-82dc-4082-917b-4657a612566e</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>BP</t>
         </is>
       </c>
     </row>
@@ -5483,25 +5595,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BCG Vaccine</t>
+          <t>Gentamicin</t>
         </is>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
+          <t>4f895d9a-7600-44c6-b867-c72af7bd7413</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Gent</t>
         </is>
       </c>
     </row>
@@ -5513,25 +5625,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>ABX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Amoxicillin</t>
+          <t>X-penicillin and gentamicin</t>
         </is>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
+          <t>27e4ad0e-ad3d-4ef1-97d0-7dfff0495574</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>ABX</t>
         </is>
       </c>
     </row>
@@ -5543,25 +5655,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Amikacin</t>
+          <t>BCG Vaccine</t>
         </is>
       </c>
       <c r="D109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
+          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>BCG</t>
         </is>
       </c>
     </row>
@@ -5573,25 +5685,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMIN</t>
+          <t>Amox</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Aminophylline</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
       <c r="D110">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>b43e9922-debb-426b-9a29-5c8e55239813</t>
+          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMIN</t>
+          <t>Amox</t>
         </is>
       </c>
     </row>
@@ -5603,25 +5715,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Amik</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ampicillin</t>
+          <t>Amikacin</t>
         </is>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>8bf190f9-958d-40b8-850a-c98e816ab3b8</t>
+          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Amik</t>
         </is>
       </c>
     </row>
@@ -5633,25 +5745,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>AMIN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AZT (Zidovudine)</t>
+          <t>Aminophylline</t>
         </is>
       </c>
       <c r="D112">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
+          <t>b43e9922-debb-426b-9a29-5c8e55239813</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>AMIN</t>
         </is>
       </c>
     </row>
@@ -5663,25 +5775,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>Amp</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Ampicillin</t>
         </is>
       </c>
       <c r="D113">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
+          <t>8bf190f9-958d-40b8-850a-c98e816ab3b8</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>Amp</t>
         </is>
       </c>
     </row>
@@ -5693,25 +5805,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>AZT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ceftriaxone</t>
+          <t>AZT (Zidovudine)</t>
         </is>
       </c>
       <c r="D114">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2c165a7b-374b-4364-b4dd-df8c48b8d3d7</t>
+          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>AZT</t>
         </is>
       </c>
     </row>
@@ -5723,25 +5835,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHLO</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chloramphenicol</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="D115">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>afd30972-9cec-46b8-93c8-86f9c225adc0</t>
+          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CHLO</t>
+          <t>CAF</t>
         </is>
       </c>
     </row>
@@ -5753,25 +5865,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cloxacillin</t>
+          <t>Ceftriaxone</t>
         </is>
       </c>
       <c r="D116">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>cff42224-f861-4330-9468-cdc903298e70</t>
+          <t>2c165a7b-374b-4364-b4dd-df8c48b8d3d7</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CEF</t>
         </is>
       </c>
     </row>
@@ -5783,25 +5895,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>CHLO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Folate</t>
+          <t>Chloramphenicol</t>
         </is>
       </c>
       <c r="D117">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
+          <t>afd30972-9cec-46b8-93c8-86f9c225adc0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>CHLO</t>
         </is>
       </c>
     </row>
@@ -5813,25 +5925,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IMI</t>
+          <t>Clox</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Imipenem</t>
+          <t>Cloxacillin</t>
         </is>
       </c>
       <c r="D118">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>9b23de8c-2e7f-4663-b504-9605d6b09c6f</t>
+          <t>cff42224-f861-4330-9468-cdc903298e70</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMI</t>
+          <t>Clox</t>
         </is>
       </c>
     </row>
@@ -5843,25 +5955,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Folate</t>
         </is>
       </c>
       <c r="D119">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
+          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -5873,25 +5985,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IMI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metronidazole</t>
+          <t>Imipenem</t>
         </is>
       </c>
       <c r="D120">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
+          <t>9b23de8c-2e7f-4663-b504-9605d6b09c6f</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IMI</t>
         </is>
       </c>
     </row>
@@ -5903,25 +6015,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nevirapine</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D121">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
+          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
@@ -5933,25 +6045,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Phenobarbitone</t>
+          <t>Metronidazole</t>
         </is>
       </c>
       <c r="D122">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
+          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -5963,25 +6075,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Procaine Penicillin</t>
+          <t>Nevirapine</t>
         </is>
       </c>
       <c r="D123">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
+          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -5993,25 +6105,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PHEN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine</t>
+          <t>Phenobarbitone</t>
         </is>
       </c>
       <c r="D124">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
+          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PHEN</t>
         </is>
       </c>
     </row>
@@ -6023,25 +6135,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vancomycin</t>
+          <t>Procaine Penicillin</t>
         </is>
       </c>
       <c r="D125">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2ca153c6-d678-445f-8ee1-a679c933737d</t>
+          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
@@ -6053,25 +6165,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>TTV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vitamin D</t>
+          <t>Tetanus Vaccine</t>
         </is>
       </c>
       <c r="D126">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
+          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>TTV</t>
         </is>
       </c>
     </row>
@@ -6083,25 +6195,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Vancomycin</t>
         </is>
       </c>
       <c r="D127">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>2ca153c6-d678-445f-8ee1-a679c933737d</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>VAN</t>
         </is>
       </c>
     </row>
@@ -6113,25 +6225,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>VITD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Vitamin D</t>
         </is>
       </c>
       <c r="D128">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>VITD</t>
         </is>
       </c>
     </row>
@@ -6143,25 +6255,25 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FLU</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Flucloxacillin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D129">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>daf84ace-b41b-45e2-8fcd-c138e8db79e2</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FLU</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -6173,25 +6285,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PCM</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paracetamol</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D130">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>c2d4e43c-293a-4377-8d40-e70911ac6212</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PCM</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -6203,115 +6315,115 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mero</t>
+          <t>FLU</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Meropenem</t>
+          <t>Flucloxacillin</t>
         </is>
       </c>
       <c r="D131">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>549ecb6a-9253-4fb6-b322-a0768a0994e2</t>
+          <t>daf84ace-b41b-45e2-8fcd-c138e8db79e2</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mero</t>
+          <t>FLU</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LMP</t>
+          <t>PCM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Last Menstrual Period (LMP)</t>
+          <t>Paracetamol</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>629168d6-09a0-4e45-83f7-f96ca3574cd6</t>
+          <t>c2d4e43c-293a-4377-8d40-e70911ac6212</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LMP</t>
+          <t>PCM</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mero</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fundal height</t>
+          <t>Meropenem</t>
         </is>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>37ceb6c2-92b9-4b6d-8565-019a630efc7f</t>
+          <t>549ecb6a-9253-4fb6-b322-a0768a0994e2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mero</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>AZT3TC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>Zidolam (AZT and 3TC)</t>
         </is>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>caa7321e-473a-41bb-98d0-fdaf3298bf81</t>
+          <t>2f8946b7-668c-4eca-aef7-217c7378a4f3</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>AZT3TC</t>
         </is>
       </c>
     </row>
@@ -6323,25 +6435,25 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EUSS</t>
+          <t>LMP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Early Ultrasound (less than 14 weeks)</t>
+          <t>Last Menstrual Period (LMP)</t>
         </is>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>987225eb-b0a5-47ca-833f-f023e6dc702e</t>
+          <t>629168d6-09a0-4e45-83f7-f96ca3574cd6</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EUSS</t>
+          <t>LMP</t>
         </is>
       </c>
     </row>
@@ -6353,25 +6465,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IVF</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IVF pregnancy</t>
+          <t>Fundal height</t>
         </is>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>5b484c0b-8184-40fe-b159-1c83cd045f06</t>
+          <t>37ceb6c2-92b9-4b6d-8565-019a630efc7f</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>IVF</t>
+          <t>FH</t>
         </is>
       </c>
     </row>
@@ -6383,25 +6495,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>USS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USS</t>
         </is>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>caa7321e-473a-41bb-98d0-fdaf3298bf81</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>USS</t>
         </is>
       </c>
     </row>
@@ -6413,25 +6525,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>EUSS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Early Ultrasound (less than 14 weeks)</t>
         </is>
       </c>
       <c r="D138">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>987225eb-b0a5-47ca-833f-f023e6dc702e</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>EUSS</t>
         </is>
       </c>
     </row>
@@ -6443,115 +6555,115 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MatSc</t>
+          <t>IVF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maturity score</t>
+          <t>IVF pregnancy</t>
         </is>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>26812489-9724-40bf-a53b-8539118af5c8</t>
+          <t>5b484c0b-8184-40fe-b159-1c83cd045f06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MatSc</t>
+          <t>IVF</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spontaneous Vaginal Delivery</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3aea8950-9c6a-48fb-af0b-14523b9a69d8</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Vacuum extraction</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1ddc4820-41ef-49d5-aa4e-69da387cb21d</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MatSc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Forceps extraction</t>
+          <t>Maturity score</t>
         </is>
       </c>
       <c r="D142">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01594970-3c95-4fbf-9a73-8beb14281ecd</t>
+          <t>26812489-9724-40bf-a53b-8539118af5c8</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MatSc</t>
         </is>
       </c>
     </row>
@@ -6563,25 +6675,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Elective Ceasarian Section (ELCS)</t>
+          <t>Spontaneous Vaginal Delivery</t>
         </is>
       </c>
       <c r="D143">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>6d8ce857-9f83-40c6-9be3-eac23212e8e6</t>
+          <t>3aea8950-9c6a-48fb-af0b-14523b9a69d8</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SVD</t>
         </is>
       </c>
     </row>
@@ -6593,25 +6705,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Emergency Ceasarian Section (EMCS)</t>
+          <t>Vacuum extraction</t>
         </is>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>e68a354c-7aa7-46eb-b5f2-79ba58cdec92</t>
+          <t>1ddc4820-41ef-49d5-aa4e-69da387cb21d</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6623,25 +6735,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Breech extraction (vaginal)</t>
+          <t>Forceps extraction</t>
         </is>
       </c>
       <c r="D145">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>fe3efc4e-3c92-4515-860b-90de2ba627e2</t>
+          <t>01594970-3c95-4fbf-9a73-8beb14281ecd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6653,25 +6765,25 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Induced Vaginal Delivery</t>
+          <t>Elective Ceasarian Section (ELCS)</t>
         </is>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2200ef02-8c6f-4fed-89f4-c1ec92adc8b4</t>
+          <t>6d8ce857-9f83-40c6-9be3-eac23212e8e6</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6683,25 +6795,25 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Elective Caesarean Section (ELCS)</t>
+          <t>Emergency Ceasarian Section (EMCS)</t>
         </is>
       </c>
       <c r="D147">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>08ca9190-6f91-40d7-a01e-1364a362a1ca</t>
+          <t>e68a354c-7aa7-46eb-b5f2-79ba58cdec92</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6713,25 +6825,25 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Emergency Caesarean Section (EMCS)</t>
+          <t>Breech extraction (vaginal)</t>
         </is>
       </c>
       <c r="D148">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1346607d-1f34-4e24-9085-317c75991a64</t>
+          <t>fe3efc4e-3c92-4515-860b-90de2ba627e2</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -6743,25 +6855,25 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Elective Caesarian Section (ELCS)</t>
+          <t>Induced Vaginal Delivery</t>
         </is>
       </c>
       <c r="D149">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6779d3ec-47f0-4a65-b206-5c3047f777a9</t>
+          <t>2200ef02-8c6f-4fed-89f4-c1ec92adc8b4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6773,25 +6885,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Emergency Caesarian Section (EMCS)</t>
+          <t>Elective Caesarean Section (ELCS)</t>
         </is>
       </c>
       <c r="D150">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>d3471b13-198e-40d4-9b9f-679098db708b</t>
+          <t>08ca9190-6f91-40d7-a01e-1364a362a1ca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6803,25 +6915,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spontaneous vaginal delivery</t>
+          <t>Emergency Caesarean Section (EMCS)</t>
         </is>
       </c>
       <c r="D151">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>9c688b11-b2f2-4fd2-85e8-95752e0c5bf8</t>
+          <t>1346607d-1f34-4e24-9085-317c75991a64</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6833,25 +6945,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IVD</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Induced vaginal delivery</t>
+          <t>Elective Caesarian Section (ELCS)</t>
         </is>
       </c>
       <c r="D152">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>82c893e6-fa9e-49c1-960a-b6327db444fa</t>
+          <t>6779d3ec-47f0-4a65-b206-5c3047f777a9</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IVD</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6863,25 +6975,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Emergency Caesarean section</t>
+          <t>Emergency Caesarian Section (EMCS)</t>
         </is>
       </c>
       <c r="D153">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>fa2fd7c3-100a-4cb8-9c67-de0d4c071ed6</t>
+          <t>d3471b13-198e-40d4-9b9f-679098db708b</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6893,25 +7005,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ElCS</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Elective Caesarean section</t>
+          <t>Spontaneous vaginal delivery</t>
         </is>
       </c>
       <c r="D154">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>430569c0-e3d6-4a9e-a08e-9a6a025e9e08</t>
+          <t>9c688b11-b2f2-4fd2-85e8-95752e0c5bf8</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ElCS</t>
+          <t>SVD</t>
         </is>
       </c>
     </row>
@@ -6923,25 +7035,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Vent</t>
+          <t>IVD</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ventouse</t>
+          <t>Induced vaginal delivery</t>
         </is>
       </c>
       <c r="D155">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>3165f6fb-49fc-4d49-9106-21b11a5abf72</t>
+          <t>82c893e6-fa9e-49c1-960a-b6327db444fa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vent</t>
+          <t>IVD</t>
         </is>
       </c>
     </row>
@@ -6953,25 +7065,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>For</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Forceps</t>
+          <t>Emergency Caesarean section</t>
         </is>
       </c>
       <c r="D156">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>8fe2997a-1171-4321-aa84-59554fb03289</t>
+          <t>fa2fd7c3-100a-4cb8-9c67-de0d4c071ed6</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>For</t>
+          <t>ECS</t>
         </is>
       </c>
     </row>
@@ -6983,115 +7095,115 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ElCS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Instrumental Delivery</t>
+          <t>Elective Caesarean section</t>
         </is>
       </c>
       <c r="D157">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>3ef78a13-e3ea-4986-8612-bd929fc3bc4b</t>
+          <t>430569c0-e3d6-4a9e-a08e-9a6a025e9e08</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ElCS</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Vent</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Discharged</t>
+          <t>Ventouse</t>
         </is>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
+          <t>3165f6fb-49fc-4d49-9106-21b11a5abf72</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Vent</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>For</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Death (at LESS than 24 hrs of age)</t>
+          <t>Forceps</t>
         </is>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
+          <t>8fe2997a-1171-4321-aa84-59554fb03289</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>For</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Death (at MORE than 24 hrs of age)</t>
+          <t>Instrumental Delivery</t>
         </is>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
+          <t>3ef78a13-e3ea-4986-8612-bd929fc3bc4b</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -7103,25 +7215,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Discharged</t>
         </is>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
+          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -7133,25 +7245,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Absconded</t>
+          <t>Death (at LESS than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D162">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
+          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
     </row>
@@ -7163,25 +7275,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Transferred to other ward</t>
+          <t>Death (at MORE than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D163">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
+          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
     </row>
@@ -7193,25 +7305,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D164">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
+          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DDA</t>
         </is>
       </c>
     </row>
@@ -7223,25 +7335,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Absconded</t>
         </is>
       </c>
       <c r="D165">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
+          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>ABS</t>
         </is>
       </c>
     </row>
@@ -7253,25 +7365,25 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Discharge on Palliative Care</t>
+          <t>Transferred to other ward</t>
         </is>
       </c>
       <c r="D166">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
+          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -7283,25 +7395,25 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D167">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
+          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>TRH</t>
         </is>
       </c>
     </row>
@@ -7313,25 +7425,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brought in dead</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D168">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
+          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>DCR</t>
         </is>
       </c>
     </row>
@@ -7343,25 +7455,25 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DPC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stillbirth</t>
+          <t>Discharge on Palliative Care</t>
         </is>
       </c>
       <c r="D169">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
+          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DPC</t>
         </is>
       </c>
     </row>
@@ -7373,25 +7485,25 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>NND</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Discharged against medical advice</t>
+          <t>Died</t>
         </is>
       </c>
       <c r="D170">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
+          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>NND</t>
         </is>
       </c>
     </row>
@@ -7403,25 +7515,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Live Birth</t>
+          <t>Brought in dead</t>
         </is>
       </c>
       <c r="D171">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
+          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BID</t>
         </is>
       </c>
     </row>
@@ -7433,25 +7545,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Early Neonatal Death</t>
+          <t>Stillbirth</t>
         </is>
       </c>
       <c r="D172">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
+          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STB</t>
         </is>
       </c>
     </row>
@@ -7463,25 +7575,25 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stillbirth Macerated</t>
+          <t>Discharged against medical advice</t>
         </is>
       </c>
       <c r="D173">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
+          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>DAMA</t>
         </is>
       </c>
     </row>
@@ -7493,25 +7605,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stillbirth Fresh</t>
+          <t>Live Birth</t>
         </is>
       </c>
       <c r="D174">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
+          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
@@ -7523,25 +7635,25 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>ENND</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
+          <t>Early Neonatal Death</t>
         </is>
       </c>
       <c r="D175">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
+          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>ENND</t>
         </is>
       </c>
     </row>
@@ -7558,15 +7670,15 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Stillbirth Mascerated</t>
+          <t>Stillbirth Macerated</t>
         </is>
       </c>
       <c r="D176">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
+          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7583,25 +7695,25 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBF</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Miscarriage - death before 22 weeks' gestation</t>
+          <t>Stillbirth Fresh</t>
         </is>
       </c>
       <c r="D177">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
+          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBF</t>
         </is>
       </c>
     </row>
@@ -7613,115 +7725,115 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Transferred to another ward (example: paediatric ward)</t>
+          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
         </is>
       </c>
       <c r="D178">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
+          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>Stillbirth Mascerated</t>
         </is>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>e04ff02c-1286-40a2-a985-ad56a7b238fb</t>
+          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>Miscarriage - death before 22 weeks' gestation</t>
         </is>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>de50fd8f-89b4-4e08-8d22-0ad82ec9e0e4</t>
+          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>Transferred to another ward (example: paediatric ward)</t>
         </is>
       </c>
       <c r="D181">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>7c072e4f-8070-4b46-b715-a31b4c37dd1c</t>
+          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -7733,25 +7845,25 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="D182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>15e12253-f7fc-4b3b-90b1-6cb0efe4bc56</t>
+          <t>e04ff02c-1286-40a2-a985-ad56a7b238fb</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
     </row>
@@ -7763,115 +7875,115 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>Brow</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brow</t>
         </is>
       </c>
       <c r="D183">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>de50fd8f-89b4-4e08-8d22-0ad82ec9e0e4</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>Brow</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>Breech</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Foetal Distress</t>
+          <t>Breech</t>
         </is>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>e5304e03-7867-44a7-8570-8957e4c97915</t>
+          <t>7c072e4f-8070-4b46-b715-a31b4c37dd1c</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>Breech</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pres</t>
+          <t>Face</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Malpresentation (e.g. breech)</t>
+          <t>Face</t>
         </is>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>d4bbfcc5-355a-4431-81a9-89664d5e38bd</t>
+          <t>15e12253-f7fc-4b3b-90b1-6cb0efe4bc56</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pres</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Scar</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Previous scar(s)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D186">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>b59e307e-3bcd-43fb-a203-1b389c4de0a3</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Scar</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
@@ -7883,25 +7995,25 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Eclampsia</t>
+          <t>Foetal Distress</t>
         </is>
       </c>
       <c r="D187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>79230ad0-5a50-4bfe-a699-1777f4b221f3</t>
+          <t>e5304e03-7867-44a7-8570-8957e4c97915</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FD</t>
         </is>
       </c>
     </row>
@@ -7913,25 +8025,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Pres</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Pre-Eclampsia</t>
+          <t>Malpresentation (e.g. breech)</t>
         </is>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>da963f3e-55cc-4c78-8a96-1857368a46a6</t>
+          <t>d4bbfcc5-355a-4431-81a9-89664d5e38bd</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Pres</t>
         </is>
       </c>
     </row>
@@ -7943,25 +8055,25 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>Scar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Fibroids</t>
+          <t>Previous scar(s)</t>
         </is>
       </c>
       <c r="D189">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>3a4978c4-8cf6-42c4-9112-c842239c440b</t>
+          <t>b59e307e-3bcd-43fb-a203-1b389c4de0a3</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>Scar</t>
         </is>
       </c>
     </row>
@@ -7973,25 +8085,25 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Big Fundus</t>
+          <t>Eclampsia</t>
         </is>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>8f4e1cfc-2ccd-41db-bf2c-055ab1e9ba05</t>
+          <t>79230ad0-5a50-4bfe-a699-1777f4b221f3</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -8003,25 +8115,25 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Mult</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Multiple gestation</t>
+          <t>Pre-Eclampsia</t>
         </is>
       </c>
       <c r="D191">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>f5a66afc-8878-448d-82cc-17b5dd56945f</t>
+          <t>da963f3e-55cc-4c78-8a96-1857368a46a6</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mult</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
@@ -8033,25 +8145,25 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prolonged labour</t>
+          <t>Fibroids</t>
         </is>
       </c>
       <c r="D192">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>c4be4934-627c-49aa-b684-78bc4de63954</t>
+          <t>3a4978c4-8cf6-42c4-9112-c842239c440b</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Fi</t>
         </is>
       </c>
     </row>
@@ -8063,25 +8175,25 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Fund</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Post Term</t>
+          <t>Big Fundus</t>
         </is>
       </c>
       <c r="D193">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>e8e2e171-8b87-4f36-8d5d-e2b89e8dadfb</t>
+          <t>8f4e1cfc-2ccd-41db-bf2c-055ab1e9ba05</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Fund</t>
         </is>
       </c>
     </row>
@@ -8093,25 +8205,25 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>Mult</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cephalopelvic Disproportion</t>
+          <t>Multiple gestation</t>
         </is>
       </c>
       <c r="D194">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>02f990a6-3622-45b8-aaa5-654c8686b180</t>
+          <t>f5a66afc-8878-448d-82cc-17b5dd56945f</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>Mult</t>
         </is>
       </c>
     </row>
@@ -8123,132 +8235,132 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Prolonged labour</t>
         </is>
       </c>
       <c r="D195">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ca00cdbe-c4c3-4dff-a5de-173001fbc6fd</t>
+          <t>c4be4934-627c-49aa-b684-78bc4de63954</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>Pr</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Booked</t>
+          <t>Post Term</t>
         </is>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6271a881-1012-4528-b6b8-b0bf9f15256e</t>
+          <t>e8e2e171-8b87-4f36-8d5d-e2b89e8dadfb</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Unbooked</t>
+          <t>Cephalopelvic Disproportion</t>
         </is>
       </c>
       <c r="D197">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2258182f-734a-494d-a6a2-0768d0eac104</t>
+          <t>02f990a6-3622-45b8-aaa5-654c8686b180</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>CPD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D198">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>8e1b1709-6e24-45f1-9b26-910e0439ccdf</t>
+          <t>ca00cdbe-c4c3-4dff-a5de-173001fbc6fd</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Stim</t>
+          <t>Bkd</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Stimulation</t>
+          <t>Booked</t>
         </is>
       </c>
       <c r="D199">
@@ -8256,29 +8368,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ca33aac1-408e-45d2-895d-4c1bdce1a60f</t>
+          <t>6271a881-1012-4528-b6b8-b0bf9f15256e</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Stim</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Suc</t>
+          <t>Ubkd</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Suctioning</t>
+          <t>Unbooked</t>
         </is>
       </c>
       <c r="D200">
@@ -8286,29 +8398,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>14af2965-3553-4e19-b699-0e65126a2644</t>
+          <t>2258182f-734a-494d-a6a2-0768d0eac104</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Suc</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D201">
@@ -8316,12 +8428,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>12200c9f-ca31-4949-9799-e49c6ab4ce1d</t>
+          <t>8e1b1709-6e24-45f1-9b26-910e0439ccdf</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -8333,25 +8445,25 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BVM</t>
+          <t>Stim</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (BVM)</t>
+          <t>Stimulation</t>
         </is>
       </c>
       <c r="D202">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>78cc28c2-1a13-46cd-a927-8f8a22a84dad</t>
+          <t>ca33aac1-408e-45d2-895d-4c1bdce1a60f</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>BVM</t>
+          <t>Stim</t>
         </is>
       </c>
     </row>
@@ -8363,25 +8475,25 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>Suc</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cardio Pulmonary Resuscitation (CPR)</t>
+          <t>Suctioning</t>
         </is>
       </c>
       <c r="D203">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>73e4b1a6-adbb-46e6-b49b-f4d3b4140ff8</t>
+          <t>14af2965-3553-4e19-b699-0e65126a2644</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>Suc</t>
         </is>
       </c>
     </row>
@@ -8393,25 +8505,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D204">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>12200c9f-ca31-4949-9799-e49c6ab4ce1d</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>O2</t>
         </is>
       </c>
     </row>
@@ -8423,25 +8535,25 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>BVM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Bag Valve Mask Ventilation (BVM)</t>
         </is>
       </c>
       <c r="D205">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>78cc28c2-1a13-46cd-a927-8f8a22a84dad</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>BVM</t>
         </is>
       </c>
     </row>
@@ -8453,25 +8565,25 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BVM9</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (less than 10 mins)</t>
+          <t>Cardio Pulmonary Resuscitation (CPR)</t>
         </is>
       </c>
       <c r="D206">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>de9112c8-6ed1-424f-9b22-53fa3311c6af</t>
+          <t>73e4b1a6-adbb-46e6-b49b-f4d3b4140ff8</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>BVM9</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -8483,25 +8595,25 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BVM10</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (Greater than 10 mins)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D207">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>93f4c9d1-e385-4448-861f-aa46f72c78d9</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>BVM10</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
@@ -8513,25 +8625,25 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ADREN</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Adrenaline</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D208">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>b6b12b8c-1130-48ce-941c-00e677dbe903</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ADREN</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -8543,25 +8655,25 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>INTUB</t>
+          <t>BVM9</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Intubation</t>
+          <t>Bag Valve Mask Ventilation (less than 10 mins)</t>
         </is>
       </c>
       <c r="D209">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1904d242-d54a-44d6-a766-1c61193b585d</t>
+          <t>de9112c8-6ed1-424f-9b22-53fa3311c6af</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>INTUB</t>
+          <t>BVM9</t>
         </is>
       </c>
     </row>
@@ -8573,25 +8685,25 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BVM10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bag Valve Mask Ventilation (Greater than 10 mins)</t>
         </is>
       </c>
       <c r="D210">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ec43c412-4d4e-40d8-a8c6-36c26ebff19f</t>
+          <t>93f4c9d1-e385-4448-861f-aa46f72c78d9</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BVM10</t>
         </is>
       </c>
     </row>
@@ -8603,115 +8715,115 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADREN</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Adrenaline</t>
         </is>
       </c>
       <c r="D211">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>6094c97b-0909-4539-bb8e-aa0da0c3f3ef</t>
+          <t>b6b12b8c-1130-48ce-941c-00e677dbe903</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADREN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INTUB</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Intubation</t>
         </is>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4e5cdd19-28a0-4dc9-94f5-d09feb56fb18</t>
+          <t>1904d242-d54a-44d6-a766-1c61193b585d</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INTUB</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tw1</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>1st Twin</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>63af2b9c-f7ed-44ef-9991-629f4a086ab5</t>
+          <t>ec43c412-4d4e-40d8-a8c6-36c26ebff19f</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tw1</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tw2</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2nd Twin</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>0be1f4af-4b4f-45f8-a3e8-3daa60a95632</t>
+          <t>6094c97b-0909-4539-bb8e-aa0da0c3f3ef</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tw2</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -8723,25 +8835,25 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tr1</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>1st Triplet</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D215">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1cdcce3b-27e0-4b70-9de5-f4da25d0c793</t>
+          <t>4e5cdd19-28a0-4dc9-94f5-d09feb56fb18</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tr1</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -8753,25 +8865,25 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tr2</t>
+          <t>Tw1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2nd Triplet</t>
+          <t>1st Twin</t>
         </is>
       </c>
       <c r="D216">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1d2569b0-6807-4007-93d4-965f3b56ce8d</t>
+          <t>63af2b9c-f7ed-44ef-9991-629f4a086ab5</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tr2</t>
+          <t>Tw1</t>
         </is>
       </c>
     </row>
@@ -8783,25 +8895,25 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tr3</t>
+          <t>Tw2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>3rd Triplet</t>
+          <t>2nd Twin</t>
         </is>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>e0ca7796-b2df-47a4-9144-3a6cc74b4859</t>
+          <t>0be1f4af-4b4f-45f8-a3e8-3daa60a95632</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tr3</t>
+          <t>Tw2</t>
         </is>
       </c>
     </row>
@@ -8813,25 +8925,25 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Tr1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1st Quadruplet</t>
+          <t>1st Triplet</t>
         </is>
       </c>
       <c r="D218">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>294280e4-e5e6-4160-982b-86ba5cdbde06</t>
+          <t>1cdcce3b-27e0-4b70-9de5-f4da25d0c793</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Tr1</t>
         </is>
       </c>
     </row>
@@ -8843,25 +8955,25 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Tr2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2nd Quadruplet</t>
+          <t>2nd Triplet</t>
         </is>
       </c>
       <c r="D219">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>3546150a-af2b-4ced-8f25-a60c25dac62d</t>
+          <t>1d2569b0-6807-4007-93d4-965f3b56ce8d</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Tr2</t>
         </is>
       </c>
     </row>
@@ -8873,25 +8985,25 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Tr3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>3rd Quadruplet</t>
+          <t>3rd Triplet</t>
         </is>
       </c>
       <c r="D220">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2b41e898-f918-4229-9390-7ea861d5ad52</t>
+          <t>e0ca7796-b2df-47a4-9144-3a6cc74b4859</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Tr3</t>
         </is>
       </c>
     </row>
@@ -8903,25 +9015,25 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>4th Quadruplet</t>
+          <t>1st Quadruplet</t>
         </is>
       </c>
       <c r="D221">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>a9f55c14-30c3-43c1-9900-9631d281ab12</t>
+          <t>294280e4-e5e6-4160-982b-86ba5cdbde06</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
     </row>
@@ -8933,125 +9045,140 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Multiple birth</t>
+          <t>2nd Quadruplet</t>
         </is>
       </c>
       <c r="D222">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>0b6d0d11-ef3b-4845-b57d-1dda870fb1f3</t>
+          <t>3546150a-af2b-4ced-8f25-a60c25dac62d</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spontaneous Vaginal Delivery (SVD)</t>
+          <t>3rd Quadruplet</t>
         </is>
       </c>
       <c r="D223">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2b41e898-f918-4229-9390-7ea861d5ad52</t>
+        </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Q3</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Booked (legacy Y)</t>
+          <t>4th Quadruplet</t>
         </is>
       </c>
       <c r="D224">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>a9f55c14-30c3-43c1-9900-9631d281ab12</t>
+        </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Booked (legacy Yes)</t>
+          <t>Multiple birth</t>
         </is>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0b6d0d11-ef3b-4845-b57d-1dda870fb1f3</t>
+        </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Twin</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Unbooked (legacy N)</t>
+          <t>Spontaneous Vaginal Delivery (SVD)</t>
         </is>
       </c>
       <c r="D226">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9063,95 +9190,95 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Unbooked (legacy No)</t>
+          <t>Booked (legacy Y)</t>
         </is>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prematurity (legacy PR)</t>
+          <t>Booked (legacy Yes)</t>
         </is>
       </c>
       <c r="D228">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Birth asphyxia / HIE (legacy BA)</t>
+          <t>Unbooked (legacy N)</t>
         </is>
       </c>
       <c r="D229">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PRRDS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Premature with respiratory distress (legacy PRRDS)</t>
+          <t>Unbooked (legacy No)</t>
         </is>
       </c>
       <c r="D230">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
@@ -9163,20 +9290,20 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Feeding difficulty (legacy FD)</t>
+          <t>Prematurity (legacy PR)</t>
         </is>
       </c>
       <c r="D231">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>Prem</t>
         </is>
       </c>
     </row>
@@ -9188,20 +9315,20 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HIVXL</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>HIV exposed low risk (legacy HIVXL)</t>
+          <t>Birth asphyxia / HIE (legacy BA)</t>
         </is>
       </c>
       <c r="D232">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIE</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9340,20 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ri</t>
+          <t>PRRDS</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Sepsis risk factors (legacy Ri)</t>
+          <t>Premature with respiratory distress (legacy PRRDS)</t>
         </is>
       </c>
       <c r="D233">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>PremRD</t>
         </is>
       </c>
     </row>
@@ -9238,20 +9365,20 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OCA</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other congenital abnormality (legacy OCA)</t>
+          <t>Feeding difficulty (legacy FD)</t>
         </is>
       </c>
       <c r="D234">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cong</t>
+          <t>DF</t>
         </is>
       </c>
     </row>
@@ -9263,18 +9390,93 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
+          <t>HIVXL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>HIV exposed low risk (legacy HIVXL)</t>
+        </is>
+      </c>
+      <c r="D235">
+        <v>74</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>HIVLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ri</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sepsis risk factors (legacy Ri)</t>
+        </is>
+      </c>
+      <c r="D236">
+        <v>75</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OCA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Other congenital abnormality (legacy OCA)</t>
+        </is>
+      </c>
+      <c r="D237">
+        <v>76</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Cong</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
           <t>BI</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Birth injury / trauma (legacy BI)</t>
         </is>
       </c>
-      <c r="D235">
-        <v>76</v>
-      </c>
-      <c r="F235" t="inlineStr">
+      <c r="D238">
+        <v>77</v>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
@@ -9751,7 +9953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9934,6 +10136,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Categorical with no value map entries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
